--- a/49794_Cuenca_Nanay/_raw_reportes_xlsx/IDConfig_65094_completo.xlsx
+++ b/49794_Cuenca_Nanay/_raw_reportes_xlsx/IDConfig_65094_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbd31686abf8849be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Raf0bd89494194f41"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,546 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49794_Cuenca_Nanay/_raw_reportes_xlsx/IDConfig_65094_completo.xlsx
+++ b/49794_Cuenca_Nanay/_raw_reportes_xlsx/IDConfig_65094_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Raf0bd89494194f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R443e321805ea4027"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2826 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
